--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{996DD11D-75BD-46B1-BFD3-8A9213CF15BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FD68506-CAF7-4C1D-82CF-E546E450CD28}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93DBBB07-DB6D-4889-BC21-2D874014B9DC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{814C7267-2295-4178-BE63-09C692C4B9EB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{001A1A76-4010-4703-A0E7-71AE39631C27}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B03DA3-D6FF-4EC7-BB31-8C57162443C7}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FD68506-CAF7-4C1D-82CF-E546E450CD28}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{712F6CE4-7B65-4270-92B4-FB8A8D7515E6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{814C7267-2295-4178-BE63-09C692C4B9EB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD38D3D2-36D4-4BAD-BD3B-C7B1C6433F28}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B03DA3-D6FF-4EC7-BB31-8C57162443C7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60EA75C6-5AA7-4247-BB36-805C2A5E2DF2}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{712F6CE4-7B65-4270-92B4-FB8A8D7515E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{590C60C8-8B2B-4514-93FB-4966007C05A2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD38D3D2-36D4-4BAD-BD3B-C7B1C6433F28}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07F10FDC-5147-4577-BE75-F0B725F5A2DF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60EA75C6-5AA7-4247-BB36-805C2A5E2DF2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAE560FC-7549-4CB6-AEEA-676CF40CF85F}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{590C60C8-8B2B-4514-93FB-4966007C05A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{257AD7C7-2A01-4771-85F4-58A4ABE4B931}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07F10FDC-5147-4577-BE75-F0B725F5A2DF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3047047C-697A-4793-83FF-099A328F1226}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAE560FC-7549-4CB6-AEEA-676CF40CF85F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3709887F-1175-4BD7-A6B9-0DB0CD53E126}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -11,6 +11,140 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="43">
+  <si>
+    <t>species_sci</t>
+  </si>
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>Handedness_index_mean</t>
+  </si>
+  <si>
+    <t>Handedness_strength_mean</t>
+  </si>
+  <si>
+    <t>Ateles fusciceps</t>
+  </si>
+  <si>
+    <t>Ateles geoffroyi</t>
+  </si>
+  <si>
+    <t>Ateles hybridus</t>
+  </si>
+  <si>
+    <t>Cercocebus torquatus</t>
+  </si>
+  <si>
+    <t>Cercopithecus diana</t>
+  </si>
+  <si>
+    <t>Cercopithecus neglectus</t>
+  </si>
+  <si>
+    <t>Gorilla gorilla</t>
+  </si>
+  <si>
+    <t>Homo sapiens</t>
+  </si>
+  <si>
+    <t>Hylobates lar</t>
+  </si>
+  <si>
+    <t>Hylobates moloch</t>
+  </si>
+  <si>
+    <t>Leontopithecus chrysomelas</t>
+  </si>
+  <si>
+    <t>Leontopithecus chrysopygus</t>
+  </si>
+  <si>
+    <t>Leontopithecus rosalia</t>
+  </si>
+  <si>
+    <t>Macaca fascicularis</t>
+  </si>
+  <si>
+    <t>Macaca nemestrina</t>
+  </si>
+  <si>
+    <t>Macaca silenus</t>
+  </si>
+  <si>
+    <t>Macaca sylvanus</t>
+  </si>
+  <si>
+    <t>Macaca tonkeana</t>
+  </si>
+  <si>
+    <t>Mandrillus sphinx</t>
+  </si>
+  <si>
+    <t>Nomascus gabriellae</t>
+  </si>
+  <si>
+    <t>Nomascus leucogenys</t>
+  </si>
+  <si>
+    <t>Pan paniscus</t>
+  </si>
+  <si>
+    <t>Pan troglodytes</t>
+  </si>
+  <si>
+    <t>Papio anubis</t>
+  </si>
+  <si>
+    <t>Papio hamadryas</t>
+  </si>
+  <si>
+    <t>Pithecia pithecia</t>
+  </si>
+  <si>
+    <t>Pongo sp.</t>
+  </si>
+  <si>
+    <t>Pongo sp.</t>
+  </si>
+  <si>
+    <t>Pygathrix cinerea</t>
+  </si>
+  <si>
+    <t>Rhinopithecus roxellana</t>
+  </si>
+  <si>
+    <t>Saimiri sciureus</t>
+  </si>
+  <si>
+    <t>Sapajus apella</t>
+  </si>
+  <si>
+    <t>Sapajus flavius</t>
+  </si>
+  <si>
+    <t>Sapajus xanthosternos</t>
+  </si>
+  <si>
+    <t>Semnopithecus entellus</t>
+  </si>
+  <si>
+    <t>Symphalangus syndactylus</t>
+  </si>
+  <si>
+    <t>Theropithecus gelada</t>
+  </si>
+  <si>
+    <t>Trachypithecus auratus</t>
+  </si>
+  <si>
+    <t>Trachypithecus hatinhensis</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,38 +488,26 @@
   <dimension ref="A1:D39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>species_sci</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Species</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Handedness_index_mean</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Handedness_strength_mean</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ateles fusciceps</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Ateles fusciceps</t>
-        </is>
+    <row r="1" spans="1:4" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
       </c>
       <c r="C2">
         <v>0.063</v>
@@ -394,16 +516,12 @@
         <v>0.798</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ateles geoffroyi</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Ateles geoffroyi</t>
-        </is>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
       </c>
       <c r="C3">
         <v>0.061</v>
@@ -412,16 +530,12 @@
         <v>0.829</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Ateles hybridus</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ateles hybridus</t>
-        </is>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
       </c>
       <c r="C4">
         <v>-0.377</v>
@@ -430,16 +544,12 @@
         <v>0.917</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Cercocebus torquatus</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Cercocebus torquatus</t>
-        </is>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
       </c>
       <c r="C5">
         <v>-0.029</v>
@@ -448,16 +558,12 @@
         <v>0.665</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Cercopithecus diana</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Cercopithecus diana</t>
-        </is>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
       </c>
       <c r="C6">
         <v>0.178</v>
@@ -466,16 +572,12 @@
         <v>0.755</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cercopithecus neglectus</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Cercopithecus neglectus</t>
-        </is>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
       </c>
       <c r="C7">
         <v>-0.258</v>
@@ -484,16 +586,12 @@
         <v>0.621</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Gorilla gorilla</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Gorilla gorilla</t>
-        </is>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
       </c>
       <c r="C8">
         <v>0.248</v>
@@ -502,16 +600,12 @@
         <v>0.541</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
       </c>
       <c r="C9">
         <v>0.761</v>
@@ -520,16 +614,12 @@
         <v>0.9429999999999999</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Hylobates lar</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Hylobates lar</t>
-        </is>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
       </c>
       <c r="C10">
         <v>-0.011</v>
@@ -538,16 +628,12 @@
         <v>0.614</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Hylobates moloch</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Hylobates moloch</t>
-        </is>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
       </c>
       <c r="C11">
         <v>-0.115</v>
@@ -556,16 +642,12 @@
         <v>0.799</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Leontopithecus chrysomelas</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Leontopithecus chrysomelas</t>
-        </is>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
       </c>
       <c r="C12">
         <v>0.151</v>
@@ -574,16 +656,12 @@
         <v>0.514</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Leontopithecus chrysopygus</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Leontopithecus chrysopygus</t>
-        </is>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
       </c>
       <c r="C13">
         <v>0.039</v>
@@ -592,16 +670,12 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Leontopithecus rosalia</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Leontopithecus rosalia</t>
-        </is>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
       </c>
       <c r="C14">
         <v>0.022</v>
@@ -610,16 +684,12 @@
         <v>0.502</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Macaca fascicularis</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Macaca fascicularis</t>
-        </is>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
       </c>
       <c r="C15">
         <v>-0.036</v>
@@ -628,16 +698,12 @@
         <v>0.6840000000000001</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Macaca nemestrina</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Macaca nemestrina</t>
-        </is>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
       </c>
       <c r="C16">
         <v>0.035</v>
@@ -646,16 +712,12 @@
         <v>0.527</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Macaca silenus</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Macaca silenus</t>
-        </is>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
       </c>
       <c r="C17">
         <v>-0.051</v>
@@ -664,16 +726,12 @@
         <v>0.467</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Macaca sylvanus</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Macaca sylvanus</t>
-        </is>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
       </c>
       <c r="C18">
         <v>-0.025</v>
@@ -682,16 +740,12 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Macaca tonkeana</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Macaca tonkeana</t>
-        </is>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
       </c>
       <c r="C19">
         <v>-0.057</v>
@@ -700,16 +754,12 @@
         <v>0.543</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Mandrillus sphinx</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Mandrillus sphinx</t>
-        </is>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>22</v>
       </c>
       <c r="C20">
         <v>0.034</v>
@@ -718,16 +768,12 @@
         <v>0.389</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Nomascus gabriellae</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Nomascus gabriellae</t>
-        </is>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
       </c>
       <c r="C21">
         <v>-0.173</v>
@@ -736,16 +782,12 @@
         <v>0.618</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Nomascus leucogenys</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Nomascus leucogenys</t>
-        </is>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
       </c>
       <c r="C22">
         <v>-0.031</v>
@@ -754,16 +796,12 @@
         <v>0.555</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Pan paniscus</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Pan paniscus</t>
-        </is>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>25</v>
       </c>
       <c r="C23">
         <v>0.044</v>
@@ -772,16 +810,12 @@
         <v>0.529</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
       </c>
       <c r="C24">
         <v>0.133</v>
@@ -790,16 +824,12 @@
         <v>0.507</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Papio anubis</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Papio anubis</t>
-        </is>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" t="s">
+        <v>27</v>
       </c>
       <c r="C25">
         <v>0.108</v>
@@ -808,16 +838,12 @@
         <v>0.527</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Papio hamadryas</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Papio hamadryas</t>
-        </is>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" t="s">
+        <v>28</v>
       </c>
       <c r="C26">
         <v>0.066</v>
@@ -826,16 +852,12 @@
         <v>0.408</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Pithecia pithecia</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Pithecia pithecia</t>
-        </is>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" t="s">
+        <v>29</v>
       </c>
       <c r="C27">
         <v>-0.385</v>
@@ -844,16 +866,12 @@
         <v>0.9340000000000001</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Pongo sp.</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Pongo sp.</t>
-        </is>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" t="s">
+        <v>31</v>
       </c>
       <c r="C28">
         <v>-0.225</v>
@@ -862,16 +880,12 @@
         <v>0.487</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Pygathrix cinerea</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Pygathrix cinerea</t>
-        </is>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" t="s">
+        <v>32</v>
       </c>
       <c r="C29">
         <v>0.165</v>
@@ -880,16 +894,12 @@
         <v>0.499</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Rhinopithecus roxellana</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Rhinopithecus roxellana</t>
-        </is>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" t="s">
+        <v>33</v>
       </c>
       <c r="C30">
         <v>-0.319</v>
@@ -898,16 +908,12 @@
         <v>0.729</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" t="s">
+        <v>34</v>
       </c>
       <c r="C31">
         <v>-0.119</v>
@@ -916,16 +922,12 @@
         <v>0.757</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Sapajus apella</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Sapajus apella</t>
-        </is>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" t="s">
+        <v>35</v>
       </c>
       <c r="C32">
         <v>-0.028</v>
@@ -934,16 +936,12 @@
         <v>0.6870000000000001</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Sapajus flavius</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Sapajus flavius</t>
-        </is>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" t="s">
+        <v>36</v>
       </c>
       <c r="C33">
         <v>-0.13</v>
@@ -952,16 +950,12 @@
         <v>0.769</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Sapajus xanthosternos</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Sapajus xanthosternos</t>
-        </is>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" t="s">
+        <v>37</v>
       </c>
       <c r="C34">
         <v>0.089</v>
@@ -970,16 +964,12 @@
         <v>0.677</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Semnopithecus entellus</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Semnopithecus entellus</t>
-        </is>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" t="s">
+        <v>38</v>
       </c>
       <c r="C35">
         <v>-0.184</v>
@@ -988,16 +978,12 @@
         <v>0.5600000000000001</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Symphalangus syndactylus</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Symphalangus syndactylus</t>
-        </is>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" t="s">
+        <v>39</v>
       </c>
       <c r="C36">
         <v>-0.048</v>
@@ -1006,16 +992,12 @@
         <v>0.482</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Theropithecus gelada</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Theropithecus gelada</t>
-        </is>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" t="s">
+        <v>40</v>
       </c>
       <c r="C37">
         <v>0.053</v>
@@ -1024,16 +1006,12 @@
         <v>0.257</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Trachypithecus auratus</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Trachypithecus auratus</t>
-        </is>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" t="s">
+        <v>41</v>
       </c>
       <c r="C38">
         <v>-0.256</v>
@@ -1042,16 +1020,12 @@
         <v>0.984</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Trachypithecus hatinhensis</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Trachypithecus hatinhensis</t>
-        </is>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" t="s">
+        <v>42</v>
       </c>
       <c r="C39">
         <v>-0.248</v>
@@ -1341,13 +1315,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{257AD7C7-2A01-4771-85F4-58A4ABE4B931}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A01B2220-48AB-4F19-B4D5-A64E282A0085}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3047047C-697A-4793-83FF-099A328F1226}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AE763C6-02BE-4D8F-A0E7-00F28AA8FF78}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3709887F-1175-4BD7-A6B9-0DB0CD53E126}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{410610E2-954B-46BE-8C7D-35BBB27467F8}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1315,13 +1315,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A01B2220-48AB-4F19-B4D5-A64E282A0085}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B9C79F5-D6F8-4639-B0E1-EC0C8D7E914B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AE763C6-02BE-4D8F-A0E7-00F28AA8FF78}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8960F49-18F7-47B5-BE58-10F49089F3EB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{410610E2-954B-46BE-8C7D-35BBB27467F8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{593ADBB6-BBD5-4F8B-890B-F5433CB2C7CC}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1315,13 +1315,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B9C79F5-D6F8-4639-B0E1-EC0C8D7E914B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2CAF320-5ECB-4191-8AFD-F54E81733EFE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8960F49-18F7-47B5-BE58-10F49089F3EB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB369484-9E96-46A0-AB60-4E422CAC7198}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{593ADBB6-BBD5-4F8B-890B-F5433CB2C7CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EFA5793-080E-4982-9435-E53F9C2B3134}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1037,291 +1037,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2CAF320-5ECB-4191-8AFD-F54E81733EFE}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB369484-9E96-46A0-AB60-4E422CAC7198}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EFA5793-080E-4982-9435-E53F9C2B3134}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1037,4 +1037,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{514BEC29-28B7-4548-9953-AE2178678C55}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BD74966-3C91-4D58-84D6-9C8CBD177D88}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A8E5CDA-A231-4059-8070-55002A631280}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1037,291 +1037,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{514BEC29-28B7-4548-9953-AE2178678C55}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BD74966-3C91-4D58-84D6-9C8CBD177D88}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A8E5CDA-A231-4059-8070-55002A631280}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1037,4 +1037,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0230687A-E5D9-4F22-9744-445991E156C4}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B581FF7-A529-4AEE-8C87-3F3E5BB0FDEB}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15D70EE2-7254-42BC-9233-AA10CE58E344}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1315,13 +1315,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0230687A-E5D9-4F22-9744-445991E156C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30E8BB9C-2FDC-481E-B580-8A93F6D28280}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B581FF7-A529-4AEE-8C87-3F3E5BB0FDEB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5301916F-9E85-4D13-8335-EC632475E1F1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15D70EE2-7254-42BC-9233-AA10CE58E344}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F93CD655-7889-4CBF-9477-48774668BBB2}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1315,13 +1315,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30E8BB9C-2FDC-481E-B580-8A93F6D28280}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43ADE38E-170C-46B1-B59D-5F500AC8DC9B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5301916F-9E85-4D13-8335-EC632475E1F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{330565A3-62DA-4FB2-8986-04091E041445}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F93CD655-7889-4CBF-9477-48774668BBB2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B83B7D7F-4261-48D2-819B-2DBA753F9160}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1315,13 +1315,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43ADE38E-170C-46B1-B59D-5F500AC8DC9B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{483889AA-FEE1-42C5-B215-0B7513136558}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{330565A3-62DA-4FB2-8986-04091E041445}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49E044D7-5790-4B2A-A575-3EFB876091DE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B83B7D7F-4261-48D2-819B-2DBA753F9160}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80966983-7C44-4692-96CE-6A5252D6947C}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1315,13 +1315,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{483889AA-FEE1-42C5-B215-0B7513136558}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A659697-337F-4DCE-AA4C-D63D561AC9F0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49E044D7-5790-4B2A-A575-3EFB876091DE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F46BEA9F-133A-42B9-B28B-28B4F0086A6B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80966983-7C44-4692-96CE-6A5252D6947C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8388D3E-388F-46C6-9A7E-8580D83EE712}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1315,13 +1315,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A659697-337F-4DCE-AA4C-D63D561AC9F0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C17D330D-6698-4519-BC05-6A40DF8CB6E2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F46BEA9F-133A-42B9-B28B-28B4F0086A6B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50E2591B-F9D1-4FFB-98FB-589655E52A5F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8388D3E-388F-46C6-9A7E-8580D83EE712}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E8826AB-415B-4372-8F59-EDA7DA74EEF2}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1037,291 +1037,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C17D330D-6698-4519-BC05-6A40DF8CB6E2}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50E2591B-F9D1-4FFB-98FB-589655E52A5F}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E8826AB-415B-4372-8F59-EDA7DA74EEF2}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1037,4 +1037,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E61885D-3EBA-4CF7-AE93-3B1F2984A2B6}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54806217-8B80-4A67-A1F7-B1DFF3DC4CB7}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6D9537F-191A-4229-9FB5-9A5659755F74}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1315,13 +1315,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E61885D-3EBA-4CF7-AE93-3B1F2984A2B6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A8E222A-442D-480B-8419-4DD430584988}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54806217-8B80-4A67-A1F7-B1DFF3DC4CB7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{986BBF79-7E76-41CF-9378-6FB2679F8942}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6D9537F-191A-4229-9FB5-9A5659755F74}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81966AA5-B48B-4791-B566-1716F6768EEB}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1315,13 +1315,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A8E222A-442D-480B-8419-4DD430584988}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1312971F-BD9E-42B1-B55D-C2955E47389F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{986BBF79-7E76-41CF-9378-6FB2679F8942}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A80A26-99F1-4147-828A-EDD03C9A290A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81966AA5-B48B-4791-B566-1716F6768EEB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3F4C78B-0C5A-4A0D-BC55-80FB2802E8AF}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1315,13 +1315,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1312971F-BD9E-42B1-B55D-C2955E47389F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A43E5174-0B5D-4D5A-8DFB-2084C01AF00D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A80A26-99F1-4147-828A-EDD03C9A290A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD1CFD2-EC44-43A8-96C8-C7330F1A6065}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3F4C78B-0C5A-4A0D-BC55-80FB2802E8AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17E0E762-7056-4AA3-AE78-DDD0237CD427}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1315,13 +1315,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A43E5174-0B5D-4D5A-8DFB-2084C01AF00D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A88C9F4F-0D93-4D62-A3B2-832BA546B8A5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD1CFD2-EC44-43A8-96C8-C7330F1A6065}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C94A855C-022C-469C-90DC-A3DD4103A3B7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17E0E762-7056-4AA3-AE78-DDD0237CD427}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5870EEC6-58BD-457D-A6D5-B88491E98DD1}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1315,13 +1315,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A88C9F4F-0D93-4D62-A3B2-832BA546B8A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{141878E2-D1D4-4633-9E8D-8D116DD6F9F3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C94A855C-022C-469C-90DC-A3DD4103A3B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{674EF7FE-736E-4DE9-BD4D-CC627022A7EE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5870EEC6-58BD-457D-A6D5-B88491E98DD1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D84A720-B5E3-499B-BDE0-92B679A744BE}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1037,291 +1037,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{141878E2-D1D4-4633-9E8D-8D116DD6F9F3}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{674EF7FE-736E-4DE9-BD4D-CC627022A7EE}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D84A720-B5E3-499B-BDE0-92B679A744BE}"/>
 </file>
--- a/____EvoM1_TraitTable/handedness.xlsx
+++ b/____EvoM1_TraitTable/handedness.xlsx
@@ -1037,4 +1037,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F346E2A4-4FF8-4BF1-B79C-0EA7F24889A2}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAAEDB63-C87E-4A4B-80F9-894764941CAA}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C64B8F8-E733-4191-9C08-B5F08384F20E}"/>
 </file>